--- a/clean_food_processed_no_scaling.xlsx
+++ b/clean_food_processed_no_scaling.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Project\skripsi\rekomendasi_makanan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\smartdiabets\smartdiabets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702E45A5-1EA8-4DB8-A708-E5B469559C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73946FC-B19C-4175-B771-61998F3C8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4607,6 +4612,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4954,8 +4960,9 @@
   <dimension ref="A1:K1490"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
